--- a/GBDS JULY FILES 2026/SCRR CALCULATOR - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/SCRR CALCULATOR - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{531C3042-3E54-4F43-AD60-D38C36A580D5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F55681C-3F4B-460D-8D1A-3223B3BB2DCF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="(JULY 2026)" sheetId="814" r:id="rId1"/>
@@ -4804,7 +4804,7 @@
         <v>9</v>
       </c>
       <c r="I4" s="115">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="J4" s="116"/>
       <c r="K4" s="21"/>
@@ -6067,7 +6067,9 @@
       <c r="F42" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="G42" s="199"/>
+      <c r="G42" s="199">
+        <v>20</v>
+      </c>
       <c r="H42" s="200"/>
       <c r="I42" s="200"/>
       <c r="J42" s="201"/>
@@ -6253,7 +6255,7 @@
       </c>
       <c r="G49" s="171">
         <f>H34+H35+H36+H37+H38+H39+H40+H41+G42+H44+H45+H46</f>
-        <v>272863</v>
+        <v>272883</v>
       </c>
       <c r="H49" s="172"/>
       <c r="I49" s="172"/>
@@ -6308,7 +6310,7 @@
       </c>
       <c r="G51" s="238">
         <f>G49-H29</f>
-        <v>-1808.5</v>
+        <v>-1788.5</v>
       </c>
       <c r="H51" s="239"/>
       <c r="I51" s="239"/>
@@ -6588,7 +6590,7 @@
         <v>9</v>
       </c>
       <c r="I4" s="115">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="J4" s="116"/>
       <c r="K4" s="21"/>
@@ -8357,7 +8359,7 @@
         <v>9</v>
       </c>
       <c r="I4" s="115">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="J4" s="116"/>
       <c r="K4" s="21"/>

--- a/GBDS JULY FILES 2026/SCRR CALCULATOR - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/SCRR CALCULATOR - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C94A01E-7C88-453E-880B-E25918760923}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB170B4A-47B6-4ABE-BC3D-9421E23561FB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="11" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="11" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="(JULY 2026)" sheetId="814" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2708" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2718" uniqueCount="160">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -637,6 +637,59 @@
   </si>
   <si>
     <t>NET SALES</t>
+  </si>
+  <si>
+    <t>151125</t>
+  </si>
+  <si>
+    <t>132786</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(SHORT)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/ OVER</t>
+    </r>
+  </si>
+  <si>
+    <t>2000006174</t>
+  </si>
+  <si>
+    <t>2000003203</t>
+  </si>
+  <si>
+    <t>2000008313</t>
+  </si>
+  <si>
+    <t>LOPEZ, GINA GRACE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                            GINA GARCE, LOPEZ</t>
   </si>
 </sst>
 </file>
@@ -2863,23 +2916,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>676276</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
       <xdr:row>54</xdr:row>
-      <xdr:rowOff>57727</xdr:rowOff>
+      <xdr:rowOff>69745</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>219076</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>85724</xdr:rowOff>
+      <xdr:colOff>161924</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>57149</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56A19C2F-590F-4A79-90FD-21BD04312A72}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B0F0C59-BC94-4AA9-9F8B-8D946DACB783}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2901,8 +2954,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="866776" y="10611427"/>
-          <a:ext cx="1162050" cy="408997"/>
+          <a:off x="1076325" y="10623445"/>
+          <a:ext cx="895349" cy="749404"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -19470,7 +19523,9 @@
       <c r="G16" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="H16" s="162"/>
+      <c r="H16" s="162">
+        <v>1326</v>
+      </c>
       <c r="I16" s="162"/>
       <c r="J16" s="162"/>
       <c r="L16" s="6">
@@ -19902,7 +19957,7 @@
       <c r="G29" s="172"/>
       <c r="H29" s="175">
         <f>H15-H16-H17-H18-H19-H20-H22-H23-H24+H26+H27+H28</f>
-        <v>196999</v>
+        <v>195673</v>
       </c>
       <c r="I29" s="176"/>
       <c r="J29" s="177"/>
@@ -20043,10 +20098,12 @@
       <c r="F34" s="12">
         <v>1000</v>
       </c>
-      <c r="G34" s="40"/>
+      <c r="G34" s="40">
+        <v>42</v>
+      </c>
       <c r="H34" s="203">
         <f t="shared" ref="H34:H39" si="2">F34*G34</f>
-        <v>0</v>
+        <v>42000</v>
       </c>
       <c r="I34" s="204"/>
       <c r="J34" s="205"/>
@@ -20077,10 +20134,12 @@
       <c r="F35" s="58">
         <v>500</v>
       </c>
-      <c r="G35" s="41"/>
+      <c r="G35" s="41">
+        <v>17</v>
+      </c>
       <c r="H35" s="203">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8500</v>
       </c>
       <c r="I35" s="204"/>
       <c r="J35" s="205"/>
@@ -20111,10 +20170,12 @@
       <c r="F36" s="12">
         <v>200</v>
       </c>
-      <c r="G36" s="37"/>
+      <c r="G36" s="37">
+        <v>6</v>
+      </c>
       <c r="H36" s="203">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="I36" s="204"/>
       <c r="J36" s="205"/>
@@ -20149,10 +20210,12 @@
       <c r="F37" s="12">
         <v>100</v>
       </c>
-      <c r="G37" s="39"/>
+      <c r="G37" s="39">
+        <v>2</v>
+      </c>
       <c r="H37" s="203">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I37" s="204"/>
       <c r="J37" s="205"/>
@@ -20185,10 +20248,12 @@
       <c r="F38" s="30">
         <v>50</v>
       </c>
-      <c r="G38" s="39"/>
+      <c r="G38" s="39">
+        <v>1</v>
+      </c>
       <c r="H38" s="203">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I38" s="204"/>
       <c r="J38" s="205"/>
@@ -20322,7 +20387,9 @@
       <c r="F42" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="G42" s="203"/>
+      <c r="G42" s="203">
+        <v>90</v>
+      </c>
       <c r="H42" s="204"/>
       <c r="I42" s="204"/>
       <c r="J42" s="205"/>
@@ -20380,9 +20447,15 @@
         <f>C44*120</f>
         <v>360</v>
       </c>
-      <c r="F44" s="37"/>
-      <c r="G44" s="62"/>
-      <c r="H44" s="187"/>
+      <c r="F44" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="G44" s="62" t="s">
+        <v>152</v>
+      </c>
+      <c r="H44" s="187">
+        <v>145329</v>
+      </c>
       <c r="I44" s="187"/>
       <c r="J44" s="187"/>
       <c r="K44" s="21"/>
@@ -20508,7 +20581,7 @@
       </c>
       <c r="G49" s="175">
         <f>H34+H35+H36+H37+H38+H39+H40+H41+G42+H44+H45+H46</f>
-        <v>0</v>
+        <v>197369</v>
       </c>
       <c r="H49" s="176"/>
       <c r="I49" s="176"/>
@@ -20559,15 +20632,15 @@
       <c r="C51" s="10"/>
       <c r="D51" s="31"/>
       <c r="F51" s="230" t="s">
-        <v>127</v>
-      </c>
-      <c r="G51" s="242">
+        <v>142</v>
+      </c>
+      <c r="G51" s="250">
         <f>G49-H29</f>
-        <v>-196999</v>
-      </c>
-      <c r="H51" s="243"/>
-      <c r="I51" s="243"/>
-      <c r="J51" s="244"/>
+        <v>1696</v>
+      </c>
+      <c r="H51" s="251"/>
+      <c r="I51" s="251"/>
+      <c r="J51" s="252"/>
       <c r="K51" s="21"/>
       <c r="O51" t="s">
         <v>86</v>
@@ -20589,10 +20662,10 @@
       <c r="C52" s="33"/>
       <c r="D52" s="45"/>
       <c r="F52" s="231"/>
-      <c r="G52" s="245"/>
-      <c r="H52" s="246"/>
-      <c r="I52" s="246"/>
-      <c r="J52" s="247"/>
+      <c r="G52" s="253"/>
+      <c r="H52" s="254"/>
+      <c r="I52" s="254"/>
+      <c r="J52" s="255"/>
       <c r="K52" s="21"/>
       <c r="O52" t="s">
         <v>87</v>
@@ -22879,7 +22952,9 @@
       <c r="G16" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="H16" s="162"/>
+      <c r="H16" s="162">
+        <v>1950</v>
+      </c>
       <c r="I16" s="162"/>
       <c r="J16" s="162"/>
       <c r="L16" s="6">
@@ -23310,7 +23385,7 @@
       <c r="G29" s="172"/>
       <c r="H29" s="175">
         <f>H15-H16-H17-H18-H19-H20-H22-H23-H24+H26+H27</f>
-        <v>213406.5</v>
+        <v>211456.5</v>
       </c>
       <c r="I29" s="176"/>
       <c r="J29" s="177"/>
@@ -23451,10 +23526,12 @@
       <c r="F34" s="12">
         <v>1000</v>
       </c>
-      <c r="G34" s="73"/>
+      <c r="G34" s="73">
+        <v>3</v>
+      </c>
       <c r="H34" s="203">
         <f>F34*G34</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="I34" s="204"/>
       <c r="J34" s="205"/>
@@ -23485,10 +23562,12 @@
       <c r="F35" s="58">
         <v>500</v>
       </c>
-      <c r="G35" s="41"/>
+      <c r="G35" s="41">
+        <v>1</v>
+      </c>
       <c r="H35" s="203">
         <f>F35*G35</f>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I35" s="204"/>
       <c r="J35" s="205"/>
@@ -23557,10 +23636,12 @@
       <c r="F37" s="12">
         <v>100</v>
       </c>
-      <c r="G37" s="39"/>
+      <c r="G37" s="39">
+        <v>3</v>
+      </c>
       <c r="H37" s="203">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I37" s="204"/>
       <c r="J37" s="205"/>
@@ -23591,10 +23672,12 @@
       <c r="F38" s="30">
         <v>50</v>
       </c>
-      <c r="G38" s="39"/>
+      <c r="G38" s="39">
+        <v>1</v>
+      </c>
       <c r="H38" s="203">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I38" s="204"/>
       <c r="J38" s="205"/>
@@ -23722,7 +23805,9 @@
       <c r="F42" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="G42" s="203"/>
+      <c r="G42" s="203">
+        <v>25</v>
+      </c>
       <c r="H42" s="204"/>
       <c r="I42" s="204"/>
       <c r="J42" s="205"/>
@@ -23780,9 +23865,15 @@
         <f>C44*120</f>
         <v>240</v>
       </c>
-      <c r="F44" s="37"/>
-      <c r="G44" s="75"/>
-      <c r="H44" s="187"/>
+      <c r="F44" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="G44" s="75" t="s">
+        <v>153</v>
+      </c>
+      <c r="H44" s="187">
+        <v>206816</v>
+      </c>
       <c r="I44" s="187"/>
       <c r="J44" s="187"/>
       <c r="K44" s="21"/>
@@ -23904,7 +23995,7 @@
       </c>
       <c r="G49" s="175">
         <f>H34+H35+H36+H37+H38+H39+H40+H41+G42+H44+H45+H46</f>
-        <v>0</v>
+        <v>210691</v>
       </c>
       <c r="H49" s="176"/>
       <c r="I49" s="176"/>
@@ -23953,15 +24044,15 @@
       <c r="C51" s="10"/>
       <c r="D51" s="31"/>
       <c r="F51" s="230" t="s">
-        <v>142</v>
-      </c>
-      <c r="G51" s="250">
+        <v>154</v>
+      </c>
+      <c r="G51" s="242">
         <f>G49-H29</f>
-        <v>-213406.5</v>
-      </c>
-      <c r="H51" s="251"/>
-      <c r="I51" s="251"/>
-      <c r="J51" s="252"/>
+        <v>-765.5</v>
+      </c>
+      <c r="H51" s="243"/>
+      <c r="I51" s="243"/>
+      <c r="J51" s="244"/>
       <c r="K51" s="21"/>
       <c r="O51" t="s">
         <v>86</v>
@@ -23983,10 +24074,10 @@
       <c r="C52" s="33"/>
       <c r="D52" s="45"/>
       <c r="F52" s="231"/>
-      <c r="G52" s="253"/>
-      <c r="H52" s="254"/>
-      <c r="I52" s="254"/>
-      <c r="J52" s="255"/>
+      <c r="G52" s="245"/>
+      <c r="H52" s="246"/>
+      <c r="I52" s="246"/>
+      <c r="J52" s="247"/>
       <c r="K52" s="21"/>
       <c r="O52" t="s">
         <v>87</v>
@@ -24304,7 +24395,7 @@
         <v>16</v>
       </c>
       <c r="G6" s="128" t="s">
-        <v>113</v>
+        <v>158</v>
       </c>
       <c r="H6" s="129"/>
       <c r="I6" s="129"/>
@@ -24629,7 +24720,10 @@
       <c r="G16" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="H16" s="162"/>
+      <c r="H16" s="162">
+        <f>612+768+648+300</f>
+        <v>2328</v>
+      </c>
       <c r="I16" s="162"/>
       <c r="J16" s="162"/>
       <c r="L16" s="6">
@@ -25061,7 +25155,7 @@
       <c r="G29" s="172"/>
       <c r="H29" s="175">
         <f>H15-H16-H17-H18-H19-H20-H22-H23-H24+H26+H27</f>
-        <v>250091.5</v>
+        <v>247763.5</v>
       </c>
       <c r="I29" s="176"/>
       <c r="J29" s="177"/>
@@ -25200,10 +25294,12 @@
       <c r="F34" s="12">
         <v>1000</v>
       </c>
-      <c r="G34" s="73"/>
+      <c r="G34" s="73">
+        <v>24</v>
+      </c>
       <c r="H34" s="203">
         <f>F34*G34</f>
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="I34" s="204"/>
       <c r="J34" s="205"/>
@@ -25234,10 +25330,12 @@
       <c r="F35" s="58">
         <v>500</v>
       </c>
-      <c r="G35" s="41"/>
+      <c r="G35" s="41">
+        <v>17</v>
+      </c>
       <c r="H35" s="203">
         <f>F35*G35</f>
-        <v>0</v>
+        <v>8500</v>
       </c>
       <c r="I35" s="204"/>
       <c r="J35" s="205"/>
@@ -25304,10 +25402,12 @@
       <c r="F37" s="12">
         <v>100</v>
       </c>
-      <c r="G37" s="39"/>
+      <c r="G37" s="39">
+        <v>1</v>
+      </c>
       <c r="H37" s="203">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I37" s="204"/>
       <c r="J37" s="205"/>
@@ -25471,7 +25571,9 @@
       <c r="F42" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="G42" s="203"/>
+      <c r="G42" s="203">
+        <v>19</v>
+      </c>
       <c r="H42" s="204"/>
       <c r="I42" s="204"/>
       <c r="J42" s="205"/>
@@ -25529,9 +25631,15 @@
         <f>C44*120</f>
         <v>120</v>
       </c>
-      <c r="F44" s="37"/>
-      <c r="G44" s="75"/>
-      <c r="H44" s="187"/>
+      <c r="F44" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="G44" s="75" t="s">
+        <v>155</v>
+      </c>
+      <c r="H44" s="187">
+        <v>61854</v>
+      </c>
       <c r="I44" s="187"/>
       <c r="J44" s="187"/>
       <c r="K44" s="21"/>
@@ -25559,9 +25667,15 @@
         <f>C45*84</f>
         <v>0</v>
       </c>
-      <c r="F45" s="37"/>
-      <c r="G45" s="75"/>
-      <c r="H45" s="187"/>
+      <c r="F45" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="G45" s="75" t="s">
+        <v>156</v>
+      </c>
+      <c r="H45" s="187">
+        <v>82788</v>
+      </c>
       <c r="I45" s="187"/>
       <c r="J45" s="187"/>
       <c r="K45" s="21"/>
@@ -25579,9 +25693,15 @@
         <f>C46*1.5</f>
         <v>0</v>
       </c>
-      <c r="F46" s="37"/>
-      <c r="G46" s="75"/>
-      <c r="H46" s="187"/>
+      <c r="F46" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="G46" s="75" t="s">
+        <v>157</v>
+      </c>
+      <c r="H46" s="187">
+        <v>70468</v>
+      </c>
       <c r="I46" s="187"/>
       <c r="J46" s="187"/>
       <c r="K46" s="21"/>
@@ -25651,7 +25771,7 @@
       </c>
       <c r="G49" s="175">
         <f>H34+H35+H36+H37+H38+H39+H40+H41+G42+H44+H45+H46+H47</f>
-        <v>0</v>
+        <v>247729</v>
       </c>
       <c r="H49" s="176"/>
       <c r="I49" s="176"/>
@@ -25702,15 +25822,15 @@
       <c r="C51" s="10"/>
       <c r="D51" s="31"/>
       <c r="F51" s="230" t="s">
-        <v>149</v>
-      </c>
-      <c r="G51" s="250">
+        <v>154</v>
+      </c>
+      <c r="G51" s="242">
         <f>G49-H29</f>
-        <v>-250091.5</v>
-      </c>
-      <c r="H51" s="251"/>
-      <c r="I51" s="251"/>
-      <c r="J51" s="252"/>
+        <v>-34.5</v>
+      </c>
+      <c r="H51" s="243"/>
+      <c r="I51" s="243"/>
+      <c r="J51" s="244"/>
       <c r="K51" s="21"/>
       <c r="O51" t="s">
         <v>86</v>
@@ -25732,10 +25852,10 @@
       <c r="C52" s="33"/>
       <c r="D52" s="45"/>
       <c r="F52" s="231"/>
-      <c r="G52" s="253"/>
-      <c r="H52" s="254"/>
-      <c r="I52" s="254"/>
-      <c r="J52" s="255"/>
+      <c r="G52" s="245"/>
+      <c r="H52" s="246"/>
+      <c r="I52" s="246"/>
+      <c r="J52" s="247"/>
       <c r="K52" s="21"/>
       <c r="O52" t="s">
         <v>87</v>
@@ -25808,7 +25928,7 @@
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="21"/>
       <c r="B57" t="s">
-        <v>114</v>
+        <v>159</v>
       </c>
       <c r="D57" s="34"/>
       <c r="F57" s="36"/>
